--- a/dados/concessionaria_municipio.xlsx
+++ b/dados/concessionaria_municipio.xlsx
@@ -9138,7 +9138,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14 11:05:11</t>
+          <t>2026-09-20 21:52:46</t>
         </is>
       </c>
     </row>

--- a/dados/concessionaria_municipio.xlsx
+++ b/dados/concessionaria_municipio.xlsx
@@ -9138,7 +9138,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20 21:52:46</t>
+          <t>2026-09-27 22:26:30</t>
         </is>
       </c>
     </row>

--- a/dados/concessionaria_municipio.xlsx
+++ b/dados/concessionaria_municipio.xlsx
@@ -9138,7 +9138,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-27 22:26:30</t>
+          <t>2026-10-04 22:40:23</t>
         </is>
       </c>
     </row>

--- a/dados/concessionaria_municipio.xlsx
+++ b/dados/concessionaria_municipio.xlsx
@@ -9138,7 +9138,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-04 22:40:23</t>
+          <t>2026-10-11 23:07:14</t>
         </is>
       </c>
     </row>

--- a/dados/concessionaria_municipio.xlsx
+++ b/dados/concessionaria_municipio.xlsx
@@ -9138,7 +9138,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11 23:07:14</t>
+          <t>2026-10-18 21:52:23</t>
         </is>
       </c>
     </row>

--- a/dados/concessionaria_municipio.xlsx
+++ b/dados/concessionaria_municipio.xlsx
@@ -9138,7 +9138,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18 21:52:23</t>
+          <t>2026-10-25 22:00:30</t>
         </is>
       </c>
     </row>
